--- a/Descarga Muestras/Historico.xlsx
+++ b/Descarga Muestras/Historico.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,12 +28,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,19 +48,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -77,7 +64,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -440,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A76"/>
+  <dimension ref="A1:A125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,14 +808,259 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" t="n">
+        <v>2310996</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2327007</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2326412</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2261909</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2327978</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2331147</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2296367</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2348537</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2348538</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2348546</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2348554</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2348555</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2348556</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2348557</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2348558</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2348559</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2348560</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2344733</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2346386</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2346391</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2350375</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2350374</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2346369</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2346380</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2350379</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2350376</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2346367</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2346364</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2346368</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2346385</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2346383</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2350373</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2346388</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2346374</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2346376</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2346372</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2350380</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2350381</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2346921</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2346926</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2329224</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2329733</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2329834</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2337009</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2328816</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2328819</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2328821</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2328822</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2328829</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
-          <t>2310996</t>
+          <t>2328835</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A76"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:A125"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Descarga Muestras/Historico.xlsx
+++ b/Descarga Muestras/Historico.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A125"/>
+  <dimension ref="A1:A133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,14 +1053,54 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" t="n">
+        <v>2328835</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1973112</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2128087</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2131999</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2132001</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2190733</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2204781</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2204783</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
-          <t>2328835</t>
+          <t>2216085</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A125"/>
+  <autoFilter ref="A1:A133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Descarga Muestras/Historico.xlsx
+++ b/Descarga Muestras/Historico.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A133"/>
+  <dimension ref="A1:A157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,14 +1093,134 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" t="n">
+        <v>2216085</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2215966</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2261330</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2262799</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2280874</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2280985</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2283556</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2283557</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2289008</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2291744</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2291748</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2292069</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2310332</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2311312</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2313088</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2313903</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2323709</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2323711</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2325011</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2329195</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2329929</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2330390</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2330516</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2337760</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
-          <t>2216085</t>
+          <t>2337762</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A133"/>
+  <autoFilter ref="A1:A157"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Descarga Muestras/Historico.xlsx
+++ b/Descarga Muestras/Historico.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,10 +52,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -64,7 +77,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -427,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A157"/>
+  <dimension ref="A1:A201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,14 +1226,234 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" t="n">
+        <v>2337762</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2266505</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2308921</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2315965</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2315967</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2318133</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2318134</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2318135</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2318161</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2318163</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2318166</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2318172</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2318181</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2318394</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2318997</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>2319000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2319112</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>2319359</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2319418</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2319753</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2319781</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2319825</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2319837</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2319884</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2319969</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>2319975</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2319976</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2319985</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2319993</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2320001</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2320074</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2320428</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2320432</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2320433</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2320440</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2320444</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>2321005</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2321349</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>2324930</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2324945</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2324950</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2324955</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2324976</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
         <is>
-          <t>2337762</t>
+          <t>2325013</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A157"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:A201"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Descarga Muestras/Historico.xlsx
+++ b/Descarga Muestras/Historico.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$249</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A201"/>
+  <dimension ref="A1:A249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1446,14 +1446,254 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" t="n">
+        <v>2325013</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2329855</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2329873</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2330382</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2337275</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2343526</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2343683</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2344996</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2344997</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2344998</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2345496</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2345499</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2345626</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>2345631</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>2350394</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>2352030</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>2352032</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>2352261</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>2353677</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>2355855</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>2356155</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>2356156</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>2356157</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>2356158</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>2356159</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>2356666</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>2356991</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2357166</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2357167</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2357174</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2357175</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2357176</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2357562</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2357565</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2357566</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2357590</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2357796</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2357802</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2357803</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2357804</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2357837</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2357847</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2357848</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2357849</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2357851</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2358108</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2358261</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2358340</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
-          <t>2325013</t>
+          <t>2358440</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A201"/>
+  <autoFilter ref="A1:A249"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Descarga Muestras/Historico.xlsx
+++ b/Descarga Muestras/Historico.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$595</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A249"/>
+  <dimension ref="A1:A595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1686,14 +1686,1744 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" t="n">
+        <v>2358440</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>2070031</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2081616</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>2127108</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2127112</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2139778</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2139784</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>2198501</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2215969</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>2216097</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2263148</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2263149</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2263150</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>2263151</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2263152</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2263153</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>2263309</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>2263310</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>2263311</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>2263312</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>2263313</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>2263319</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>2263321</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>2263322</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>2263323</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>2263324</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>2263325</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>2263496</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>2263497</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>2263498</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>2263499</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>2263501</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>2263502</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>2263505</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>2263506</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>2263507</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>2263509</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>2263511</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>2263512</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>2263918</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>2263919</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>2272620</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>2272626</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>2272648</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>2273251</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>2273407</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>2273408</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>2273409</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>2274615</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>2274616</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>2274617</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>2274618</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>2274619</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>2274620</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>2274621</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>2280873</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>2291830</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>2291832</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>2291833</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>2291835</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>2308287</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>2308288</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>2308289</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>2308604</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>2308756</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>2316470</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>2318268</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>2318323</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>2318330</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>2318333</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>2318342</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>2318993</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>2319001</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>2319037</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>2319262</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>2319263</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>2319358</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>2319521</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>2319651</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>2319660</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>2319769</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>2319808</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>2319955</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>2319958</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>2320003</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>2320054</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>2320059</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>2320060</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>2320423</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>2320486</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>2320487</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>2320488</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>2320489</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>2320490</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>2320491</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>2325981</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>2325987</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>2327004</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>2327946</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>2327947</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>2327948</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>2327949</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>2327994</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>2327996</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>2328085</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>2329209</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>2329210</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>2329211</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>2329212</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>2329213</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>2329214</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>2329215</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>2329223</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>2329260</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>2329267</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>2329309</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>2329310</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>2329311</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>2329322</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>2329328</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>2329329</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>2329426</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>2329430</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>2329436</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>2329509</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>2329511</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>2329512</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>2329513</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>2329514</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>2329542</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>2329543</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>2329586</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>2329590</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>2329597</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>2329636</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>2329685</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>2329729</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>2329775</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>2329829</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>2329848</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>2329866</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>2329908</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>2330023</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>2330038</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>2330163</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>2330168</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>2330172</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>2330176</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>2330181</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>2330186</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>2330189</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>2330206</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>2330207</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>2330208</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>2330209</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>2330210</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>2330212</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>2330213</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>2330231</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>2330234</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>2330269</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>2330314</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>2330324</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>2330330</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>2330340</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>2330347</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>2330613</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>2330617</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>2330621</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>2330625</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>2330718</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>2331815</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>2332144</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>2332357</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>2332363</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>2342063</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>2347437</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>2349745</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>2349747</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>2349945</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>2350656</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>2350658</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>2350760</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>2351535</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>2351965</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>2353041</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>2353045</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>2353047</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>2353051</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>2353055</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>2353056</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>2357171</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>2357172</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>2357173</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>2357845</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>2357846</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>2359774</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>2359775</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>2359826</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>2359827</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>2359828</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>2360840</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>2360911</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>2361146</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>2361147</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>2361148</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>2361184</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>2361233</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>2361992</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>2362192</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>2362193</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>2362310</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>2362328</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>2362330</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>2362395</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>2362396</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>2362397</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>2362398</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>2362399</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>2362400</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>2362412</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>2362413</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>2362414</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>2362415</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>2362416</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>2362417</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>2362437</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>2362444</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>2362452</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>2362453</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>2362454</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>2362456</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>2362464</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>2362465</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>2362470</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>2362472</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>2362478</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>2362483</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>2362518</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>2362953</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>2362974</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>2364581</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>2365285</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>2365998</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>2366186</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>2366322</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>2366323</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>2366324</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>2366325</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>2366326</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>2366327</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>2367596</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>2368217</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>2368293</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>2368416</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>2368417</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>2368424</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>2369035</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>2369036</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>2369037</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>2369038</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>2369039</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>2369317</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>2369318</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>2369693</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>2370103</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>2370104</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>2370738</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>2370739</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>2370740</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>2371006</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>2372886</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>2373015</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>2373016</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>2373017</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>2373021</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>2373022</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>2373024</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>2373026</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>2373027</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>2373631</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>2373870</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>2373872</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>2373874</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>2373875</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>2373876</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>2373877</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>2373878</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>2373879</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>2373880</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>2373882</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>2373884</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>2373885</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>2373886</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>2373887</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>2373888</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>2373892</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>2373894</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>2373896</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>2373897</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>2373899</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>2374987</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>2375192</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>2375193</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>2375231</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>2375237</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>2375327</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>2375356</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>2375359</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>2376547</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>2377108</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>2377109</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>2377110</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>2377229</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>2377264</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>2377372</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>2377519</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>2378213</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>2378633</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>2378634</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>2378635</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>2378636</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>2378637</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>2378638</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>2378639</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>2378717</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>2378724</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>2378727</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>2378732</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>2378739</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>2378745</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>2378823</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>2378830</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>2378831</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>2378832</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>2378837</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>2378838</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>2378840</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>2378843</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>2378855</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>2378929</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>2378932</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>2378933</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>2378935</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>2378939</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>2378942</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
-          <t>2358440</t>
+          <t>2378943</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A249"/>
+  <autoFilter ref="A1:A595"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Descarga Muestras/Historico.xlsx
+++ b/Descarga Muestras/Historico.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$595</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$818</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A595"/>
+  <dimension ref="A1:A818"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3416,14 +3416,1129 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" t="inlineStr">
+      <c r="A595" t="n">
+        <v>2378943</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>2034418</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>2034419</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>2034420</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>2034421</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>2034422</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>2034423</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>2175777</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>2175778</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>2175779</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>2175780</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>2279539</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>2279540</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>2281734</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>2281736</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>2309355</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>2320957</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>2372060</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>2372061</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>2380873</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>2380874</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>2380875</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>2380877</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>2398167</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>2405457</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>2405460</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>2405462</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>2405464</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>2406323</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>2406327</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>2416236</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>2416243</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>2416247</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>2417389</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>2417390</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>2417391</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>2435454</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>2439425</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>2439427</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>2439428</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>2440986</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>2441468</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>2441635</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>2441966</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>2443212</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>2443213</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>2443214</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>2443215</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>2443217</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>2443218</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>2445705</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>2445712</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>2445750</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>2446369</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>2446658</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>2447318</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>2451272</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>2453459</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>2453479</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>2453482</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>2453485</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>2453489</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>2453490</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>2453491</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>2453492</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>2454239</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>2454690</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>2455281</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>2455789</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>2455830</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>2457138</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>2457139</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>2458571</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>2458572</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>2458573</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>2458574</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>2458576</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>2458578</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>2461235</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>2461239</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>2461479</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>2464272</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>2464273</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>2464274</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>2464275</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>2464278</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>2464281</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>2464282</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>2465574</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>2467708</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>2467710</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>2467712</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>2467714</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>2467717</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>2467718</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>2467792</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>2467794</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>2467796</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>2467798</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>2467800</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>2467805</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>2467832</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>2467833</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>2467834</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>2467835</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>2467836</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>2467837</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>2467851</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>2467854</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="n">
+        <v>2467856</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>2467857</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>2467863</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>2467864</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>2467865</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>2467866</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>2467867</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>2467868</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>2467941</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>2467944</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>2467948</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>2467950</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>2467952</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>2467954</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>2468684</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>2468685</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>2468686</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>2468687</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>2468688</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>2468689</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>2470034</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>2470036</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>2470037</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>2470038</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>2470039</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>2470040</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>2470063</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>2470086</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>2470169</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>2470170</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>2470171</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>2470172</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>2470173</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>2470174</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>2470190</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>2470810</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>2470811</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>2470812</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>2471454</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>2471473</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>2472231</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>2472289</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>2472612</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>2472613</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>2472614</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>2472616</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>2472641</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>2472644</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>2472647</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>2472649</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="n">
+        <v>2472651</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="n">
+        <v>2472683</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="n">
+        <v>2472684</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="n">
+        <v>2472685</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="n">
+        <v>2472686</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="n">
+        <v>2472687</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="n">
+        <v>2472688</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="n">
+        <v>2472937</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>2472938</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>2472940</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>2472942</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>2472944</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>2472945</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>2472947</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>2472949</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>2472950</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>2472951</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>2472954</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>2472973</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>2477264</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>2477541</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>2477550</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>2482011</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>2482054</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="n">
+        <v>2482911</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="n">
+        <v>2482930</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>2483599</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>2486099</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>2486163</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>2486166</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>2486245</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>2486568</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>2486570</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>2486820</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="n">
+        <v>2487544</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="n">
+        <v>2487589</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="n">
+        <v>2487913</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="n">
+        <v>2488428</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="n">
+        <v>2488429</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="n">
+        <v>2488430</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="n">
+        <v>2488431</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="n">
+        <v>2488432</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="n">
+        <v>2488433</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="n">
+        <v>2488434</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>2488435</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>2488436</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>2488437</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>2488569</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>2488587</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>2488619</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>2488627</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>2488643</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>2489339</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="n">
+        <v>2489340</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="n">
+        <v>2489342</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="n">
+        <v>2489343</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="n">
+        <v>2489344</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="n">
+        <v>2489345</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="n">
+        <v>2489346</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="n">
+        <v>2489469</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="n">
+        <v>2490181</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="n">
+        <v>2490202</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="n">
+        <v>2490203</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="n">
+        <v>2490262</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
         <is>
-          <t>2378943</t>
+          <t>2490338</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A595"/>
+  <autoFilter ref="A1:A818"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>